--- a/testData/Opencart_LoginData.xlsx
+++ b/testData/Opencart_LoginData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ExcelDemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5448DBDB-9ABA-463B-B0D6-73D12DF65D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A882FA33-1512-49C5-A813-E3041A372199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{395AE364-B41D-4B3C-82A9-843EC0F982D7}"/>
   </bookViews>
@@ -141,7 +141,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -156,9 +156,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -552,10 +549,10 @@
       <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
